--- a/survey_templates/048_friendship_survey--survey_templates.xlsx
+++ b/survey_templates/048_friendship_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>self_disclosure</t>
+          <t>self_disclosure_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>friendship_quality</t>
+          <t>friendship_quality_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>what do you value most in a friendship?</t>
+          <t>Friendship Quality 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>self_helpfulness</t>
+          <t>self_helpfulness_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>support_needs</t>
+          <t>support_needs_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>what do you need from friends?</t>
+          <t>Support Needs 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>self_concept</t>
+          <t>self_concept_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>what do you think about yourself in a friendship?</t>
+          <t>Self Concept 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>self_maintenance</t>
+          <t>self_maintenance_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>how do you maintain friendships?</t>
+          <t>Self Maintenance 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>self_disclosure_choices</t>
+          <t>self_disclosure_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>self_disclosure_choices</t>
+          <t>self_disclosure_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>friendship_quality_choices</t>
+          <t>friendship_quality_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>friendship_quality_choices</t>
+          <t>friendship_quality_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>self_helpfulness_choices</t>
+          <t>self_helpfulness_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>self_helpfulness_choices</t>
+          <t>self_helpfulness_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>support_needs_choices</t>
+          <t>support_needs_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>support_needs_choices</t>
+          <t>support_needs_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>self_concept_choices</t>
+          <t>self_concept_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>self_concept_choices</t>
+          <t>self_concept_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
